--- a/EbolaDiseaseAnalysisinKenya.xlsx
+++ b/EbolaDiseaseAnalysisinKenya.xlsx
@@ -4,19 +4,21 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_Sheet1A1J51" hidden="1">Sheet1!$A$1:$J$51</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Sheet1A1J511" hidden="1">Sheet1!$A$1:$J$51</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="47" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +49,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Sheet1A1J51"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Sheet1A1J511"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="59">
   <si>
     <t>NO</t>
   </si>
@@ -222,6 +224,18 @@
   <si>
     <t>Sum of CONFIRMED CASES PER 100K</t>
   </si>
+  <si>
+    <t>The highest number of confirmed cases across the weeks was 3</t>
+  </si>
+  <si>
+    <t>There is correlation between the population of a given place and the number of suspected cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum number of suspected cases contributed 65%,probable cases 17%,confirmed and recovered cases </t>
+  </si>
+  <si>
+    <t>7% each while death cases contributed 4 %</t>
+  </si>
 </sst>
 </file>
 
@@ -287,6 +301,3951 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MAX</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$55:$I$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8B79-40F5-A4A7-A0ECD70709ED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>CONFIRMED CASES</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D9A9-4D2F-9971-DC1055210388}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="999976863"/>
+        <c:axId val="999987263"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="999976863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="999987263"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="999987263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="999976863"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>POPULATION VS SUSPECTED CASES</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>850000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>897000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>944000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>991000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1038000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1085000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1132000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1179000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1226000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1273000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1320000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1367000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1414000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1461000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1508000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1555000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1602000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1649000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1696000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1743000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1790000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1837000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1884000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1931000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1978000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2072000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2119000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>866000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>913000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>960000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1007000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1054000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1101000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1148000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1195000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1242000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1289000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1336000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1383000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1430000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1477000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1524000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1571000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1618000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1665000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1712000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1759000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1806000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1853000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1DF4-4A1C-8B0D-1E3A0763BB59}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1019835744"/>
+        <c:axId val="1019851968"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1019835744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1019851968"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1019851968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1019835744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MAX</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8884-4353-ACD8-D3477068ABF8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-8884-4353-ACD8-D3477068ABF8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-8884-4353-ACD8-D3477068ABF8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-8884-4353-ACD8-D3477068ABF8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-8884-4353-ACD8-D3477068ABF8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$55:$I$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-8884-4353-ACD8-D3477068ABF8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,7 +4383,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:H14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
@@ -3031,5 +6990,37 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B16:L35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>